--- a/ex02_HRCT_dict.xlsx
+++ b/ex02_HRCT_dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\BSA 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4882AD2-F030-45F4-9FF3-23EDBEBFA443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706342D3-4D09-4880-85C9-3F77277C65CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="100">
   <si>
     <t>Сущность</t>
   </si>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t>payment_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Расписание (timetable)</t>
@@ -426,11 +423,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1241,11 +1238,11 @@
       <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="4">
+        <v>5</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>36</v>
@@ -1254,7 +1251,7 @@
         <v>35</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>6</v>
@@ -1270,10 +1267,10 @@
         <v>54</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>57</v>
@@ -1289,7 +1286,7 @@
         <v>58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>58</v>
@@ -1693,14 +1690,14 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
@@ -1715,124 +1712,124 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
